--- a/test-output/projectResourcesOutputs/GymsData.xlsx
+++ b/test-output/projectResourcesOutputs/GymsData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>Serial Number</t>
   </si>
@@ -23,22 +23,22 @@
     <t>Gym Phone Number</t>
   </si>
   <si>
-    <t>Berlin Fitness</t>
-  </si>
-  <si>
-    <t>09008644895</t>
-  </si>
-  <si>
     <t>Star Fitness Studio</t>
   </si>
   <si>
     <t>08792071271</t>
   </si>
   <si>
-    <t>D'Shoolin Functional Strength &amp; therapy</t>
+    <t>Iron Forge Gym</t>
   </si>
   <si>
-    <t>08401744248</t>
+    <t>08867792622</t>
+  </si>
+  <si>
+    <t>Krish's Fitness Pro</t>
+  </si>
+  <si>
+    <t>08296044098</t>
   </si>
   <si>
     <t>Vivek Teja's Human Weapon Fitness And Martial Arts</t>
@@ -47,10 +47,16 @@
     <t>09845459437</t>
   </si>
   <si>
-    <t>Iron Forge Gym</t>
+    <t>6E GYMS</t>
   </si>
   <si>
-    <t>08867792622</t>
+    <t>07490833660</t>
+  </si>
+  <si>
+    <t>D'Shoolin Functional Strength &amp; therapy</t>
+  </si>
+  <si>
+    <t>08401744248</t>
   </si>
 </sst>
 </file>
@@ -95,7 +101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -164,6 +170,17 @@
         <v>12</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/test-output/projectResourcesOutputs/GymsData.xlsx
+++ b/test-output/projectResourcesOutputs/GymsData.xlsx
@@ -41,22 +41,22 @@
     <t>08296044098</t>
   </si>
   <si>
-    <t>Vivek Teja's Human Weapon Fitness And Martial Arts</t>
+    <t>Berlin Fitness</t>
   </si>
   <si>
-    <t>09845459437</t>
-  </si>
-  <si>
-    <t>6E GYMS</t>
-  </si>
-  <si>
-    <t>07490833660</t>
+    <t>09008644895</t>
   </si>
   <si>
     <t>D'Shoolin Functional Strength &amp; therapy</t>
   </si>
   <si>
     <t>08401744248</t>
+  </si>
+  <si>
+    <t>Vivek Teja's Human Weapon Fitness And Martial Arts</t>
+  </si>
+  <si>
+    <t>09845459437</t>
   </si>
 </sst>
 </file>
